--- a/output/full_scan/batch_seq0_2026-06-30.xlsx
+++ b/output/full_scan/batch_seq0_2026-06-30.xlsx
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>8383</v>
+        <v>8222</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>千附</t>
+          <t>寶一</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>857.1576256970947</v>
+        <v>1089.470325637975</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>65.40000000000001</v>
+        <v>39.2</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,16 +552,16 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>61.33692603609023</v>
+        <v>62.66734604728454</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>19.51448173456839</v>
+        <v>14.25572014772759</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>1.94258640163542</v>
+        <v>4.547032563797522</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.3521904273694429</v>
+        <v>0.2547831662779135</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, volume_break, rsi_strong, breakout_20d, market_above_ma60, hist_turn_positive, foreign_buy_3d, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>8222</v>
+        <v>8383</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>寶一</t>
+          <t>千附</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>769.4703256379752</v>
+        <v>1077.157625697095</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>39.2</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>62.66734591382694</v>
+        <v>61.33692602554578</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>14.25572000268356</v>
+        <v>19.51448175691363</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>4.547032563797522</v>
+        <v>1.94258640163542</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.2547831666213414</v>
+        <v>0.3521904273694429</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, rsi_strong, breakout_20d, market_above_ma60, hist_turn_positive, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>8261</v>
+        <v>8069</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>富鼎</t>
+          <t>元太</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>731.6924026764787</v>
+        <v>1020.853617435036</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>270.5</v>
+        <v>214.5</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,29 +658,29 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>73.60041692936855</v>
+        <v>58.18498792077065</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>46.15421053290494</v>
+        <v>19.60571902489336</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.6192005278669652</v>
+        <v>3.152279933906075</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>5.85772550024334</v>
+        <v>0.1898326703734593</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, stronger_than_market, invest_trust_buy_2d, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>724.8160853651069</v>
+        <v>974.8160853651068</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>50</v>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>60.90975496866661</v>
+        <v>60.90975500945712</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>38.24439040531657</v>
+        <v>38.24439045928792</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>0.7080435736940421</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,11 +729,11 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.4440369583757872</v>
+        <v>-0.4440369584044026</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>718.8471482612923</v>
+        <v>938.8471482612924</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>31.1</v>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>66.24768441064725</v>
+        <v>66.2476844263599</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>44.6726853135988</v>
+        <v>44.67268535014065</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>0.6037799956229774</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.182963456502549</v>
+        <v>0.1829634564643898</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>8069</v>
+        <v>8163</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>元太</t>
+          <t>達方</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>705.8536174350357</v>
+        <v>921.6664880223508</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>214.5</v>
+        <v>41.7</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>58.18498802092794</v>
+        <v>54.05076296993269</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>19.60571891436357</v>
+        <v>38.64948830414162</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>3.152279933906075</v>
+        <v>0.4117039862450198</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1898326697056599</v>
+        <v>-0.7613456148663724</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>8163</v>
+        <v>8227</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>達方</t>
+          <t>巨有科技</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>696.6664880223509</v>
+        <v>898.2536725666454</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>41.7</v>
+        <v>214.5</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,49 +870,49 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>54.05076291944613</v>
+        <v>60.59429538564985</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>38.64948822054477</v>
+        <v>17.40267363745311</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.4117039862450198</v>
+        <v>3.257558473080421</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.7613456147805149</v>
+        <v>1.968754851952529</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>8081</v>
+        <v>8261</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>致新</t>
+          <t>富鼎</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>696.5050733920142</v>
+        <v>881.6924026764787</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>313</v>
+        <v>270.5</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>57.7400658356656</v>
+        <v>73.600416925719</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>27.28526420894064</v>
+        <v>46.15421041190167</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.8003189638668542</v>
+        <v>0.6192005278669652</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.9104935519548788</v>
+        <v>5.857725500796661</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>8054</v>
+        <v>8183</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>安國</t>
+          <t>精星</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>672.718245963703</v>
+        <v>857.1354816266872</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>119</v>
+        <v>34.55</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>56.92938229844581</v>
+        <v>61.48277156555344</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>23.40182449647865</v>
+        <v>18.00772723589692</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.7150016002960378</v>
+        <v>1.813548162668725</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>1.737024548672251</v>
+        <v>0.2629844754625255</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>8091</v>
+        <v>9105</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>翔名</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>651.8666925139948</v>
+        <v>818.8586469122055</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>271.5</v>
+        <v>9.49</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>57.19842248765944</v>
+        <v>54.0998527197336</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>31.19259220043713</v>
+        <v>36.62560395221698</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.189179726467043</v>
+        <v>0.3418650437127796</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-0.8671817010303933</v>
+        <v>-0.1904486917670329</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>9105</v>
+        <v>8081</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>泰金寶-DR</t>
+          <t>致新</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>648.8586469122055</v>
+        <v>811.5050733920142</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>9.49</v>
+        <v>313</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>54.09985265991357</v>
+        <v>57.74006585549965</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>36.62560395221698</v>
+        <v>27.28526419216695</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.3418650437127796</v>
+        <v>0.8003189638668542</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-0.1904486917822947</v>
+        <v>0.9104935516686474</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>8110</v>
+        <v>9905</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>華東</t>
+          <t>大華</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>646.5567516203964</v>
+        <v>798.1398791220953</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>57.3</v>
+        <v>21.3</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>50.94972934261319</v>
+        <v>64.09542066642084</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>20.0608476137136</v>
+        <v>18.90108623776633</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.4232741162068503</v>
+        <v>2.413987912209525</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-0.3463800904870735</v>
+        <v>0.0578734692177887</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>8162</v>
+        <v>8054</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>微矽電子-創</t>
+          <t>安國</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>631.945047405837</v>
+        <v>787.7182459637031</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>79.2</v>
+        <v>119</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,49 +1188,49 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>57.62054528590053</v>
+        <v>56.9293823701448</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>41.00401105289828</v>
+        <v>23.40182449657068</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.3355686167159738</v>
+        <v>0.7150016002960378</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-0.2064235150151798</v>
+        <v>1.737024548576847</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>8227</v>
+        <v>8091</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>巨有科技</t>
+          <t>翔名</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>623.2536725666454</v>
+        <v>761.8666925139948</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>214.5</v>
+        <v>271.5</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>60.59429532430911</v>
+        <v>57.19842249629135</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>17.40267359983094</v>
+        <v>31.19259219663252</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>3.257558473080421</v>
+        <v>1.189179726467043</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>1.968754852715684</v>
+        <v>-0.8671817006488549</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>8183</v>
+        <v>8105</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>精星</t>
+          <t>凌巨</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>612.1354816266872</v>
+        <v>761.1513671806255</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>34.55</v>
+        <v>22.85</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>61.48277145015105</v>
+        <v>58.959954137038</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>18.00772727340505</v>
+        <v>42.20289306020799</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.813548162668725</v>
+        <v>0.4748904527802346</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.2629844754911472</v>
+        <v>-0.0733533197676501</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>8105</v>
+        <v>8299</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>凌巨</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>591.1513671806255</v>
+        <v>741.7137050039163</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>22.85</v>
+        <v>2385</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,49 +1347,49 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>58.95995413487516</v>
+        <v>49.55019907621379</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>42.20289302955897</v>
+        <v>11.82155258979834</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.4748904527802346</v>
+        <v>0.4404001054598219</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-0.0733533197676501</v>
+        <v>-13.73207673644723</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market, kd_golden_cross, obv_uptrend, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>9136</v>
+        <v>8215</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>巨騰-DR</t>
+          <t>明基材</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>588.8717288543772</v>
+        <v>731.6741322391005</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>14.1</v>
+        <v>30.35</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>52.0836061421328</v>
+        <v>53.54425558439431</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>42.99649003355627</v>
+        <v>24.18753691928206</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.2219482871222466</v>
+        <v>0.4584924509075834</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-0.6559310953439668</v>
+        <v>-0.1889843900874377</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>8926</v>
+        <v>8466</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>美吉吉-KY</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>585.3656239116191</v>
+        <v>718.7234011200849</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>76.3</v>
+        <v>16.65</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>58.64251307885083</v>
+        <v>60.66616030522601</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>48.52499652193434</v>
+        <v>16.50708143625681</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.6133388273938272</v>
+        <v>1.175764334169687</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-0.8211857509950207</v>
+        <v>0.0747049793637507</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>8088</v>
+        <v>8926</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>品安</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>581.7471031715975</v>
+        <v>700.3656239116191</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>64.7</v>
+        <v>76.3</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,49 +1506,49 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>54.77849334294154</v>
+        <v>58.642513092959</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>25.54322967284803</v>
+        <v>48.52499646444542</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.2725380095056748</v>
+        <v>0.6133388273938272</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>-0.393005605639527</v>
+        <v>-0.8211857509759284</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>8131</v>
+        <v>8088</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>福懋科</t>
+          <t>品安</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>577.364409156485</v>
+        <v>691.7471031715975</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>72</v>
+        <v>64.7</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>51.15454127670382</v>
+        <v>54.77849339953495</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>13.79302682938896</v>
+        <v>25.54322962363126</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.5849207772849453</v>
+        <v>0.2725380095056748</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,11 +1577,11 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-0.5502133212017499</v>
+        <v>-0.3930056058493987</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>576.3919869333881</v>
+        <v>691.391986933388</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>92.40000000000001</v>
@@ -1612,10 +1612,10 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>49.88599536037438</v>
+        <v>49.88599537219617</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>23.24205379032949</v>
+        <v>23.24205381888271</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>0.5995096662554421</v>
@@ -1624,37 +1624,37 @@
         <v>0</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-0.8325043315829102</v>
+        <v>-0.8325043315638343</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>8215</v>
+        <v>8482</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>明基材</t>
+          <t>商億-KY</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>571.6741322391005</v>
+        <v>686.8948360313436</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>30.35</v>
+        <v>50</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>53.54425557414884</v>
+        <v>51.99469880208918</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>24.18753688322434</v>
+        <v>8.259741390830463</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.4584924509075834</v>
+        <v>2.04181880461479</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-0.1889843899920426</v>
+        <v>0.5518244434169968</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>8473</v>
+        <v>8109</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>山林水</t>
+          <t>博大</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>539.8214688460258</v>
+        <v>677.8597261902911</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>50.4</v>
+        <v>123.5</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>57.08603812448641</v>
+        <v>54.81150741834409</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>26.68260509350688</v>
+        <v>23.13358735023456</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.2767064489077715</v>
+        <v>0.4401116643442047</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-0.7712093157424915</v>
+        <v>-0.0961313349658838</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>8072</v>
+        <v>8473</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>陞泰</t>
+          <t>山林水</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>535.9724160298897</v>
+        <v>674.8214688460258</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>29.3</v>
+        <v>50.4</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>51.4521509998734</v>
+        <v>57.08603817004854</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>24.42232103204196</v>
+        <v>26.68260511170113</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.2220424777542141</v>
+        <v>0.2767064489077715</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-0.0587393385281496</v>
+        <v>-0.7712093157806472</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>8466</v>
+        <v>8049</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>美吉吉-KY</t>
+          <t>晶采</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>528.7234011200849</v>
+        <v>665.648308608769</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>16.65</v>
+        <v>27.4</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>60.66616030522601</v>
+        <v>53.9621753059936</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>16.50708151865168</v>
+        <v>27.19494941578463</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.175764334169687</v>
+        <v>0.6168700906424749</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.0747049793637507</v>
+        <v>-0.0125818452640558</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>8482</v>
+        <v>8110</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>商億-KY</t>
+          <t>華東</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>526.8948360313479</v>
+        <v>656.5567516203964</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>50</v>
+        <v>57.3</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>51.99469878843858</v>
+        <v>50.94972934640563</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>8.259741444196868</v>
+        <v>20.0608476137136</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>2.04181880461479</v>
+        <v>0.4232741162068503</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.5518244440466185</v>
+        <v>-0.3463800904870735</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, volume_break, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>8070</v>
+        <v>8234</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>新漢</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>525.7807290244289</v>
+        <v>653.5630474231848</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>53.6</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>47.28621150095348</v>
+        <v>56.83112433672186</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>23.41780063967209</v>
+        <v>19.66385884968909</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.1904646259093755</v>
+        <v>0.950711994117117</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.872435799899673</v>
+        <v>0.4925173473507046</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>8049</v>
+        <v>8070</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>晶采</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>525.648308608769</v>
+        <v>640.7807290244289</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>27.4</v>
+        <v>53.6</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,49 +1983,49 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>53.96217528402611</v>
+        <v>47.28621153429695</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>27.19494947472113</v>
+        <v>23.41780065097189</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.6168700906424749</v>
+        <v>0.1904646259093755</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M29" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-0.0125818452735908</v>
+        <v>-0.872435799899673</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>8050</v>
+        <v>8182</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>廣積</t>
+          <t>加高</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>518.2425455310257</v>
+        <v>635.157572834106</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>52.3</v>
+        <v>49.1</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>44.33644273342656</v>
+        <v>52.78955736323011</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>30.50847430311783</v>
+        <v>24.17410141567861</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.4675725361014795</v>
+        <v>0.4986798822405933</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.971753799016262</v>
+        <v>-0.637570252357901</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>8454</v>
+        <v>8162</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>富邦媒</t>
+          <t>微矽電子-創</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>516.1890193455164</v>
+        <v>631.945047405837</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>297.5</v>
+        <v>79.2</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>48.3844121090855</v>
+        <v>57.62054528655597</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45.41615931152405</v>
+        <v>41.00401106790765</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.8276407544254143</v>
+        <v>0.3355686167159738</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-11.00682116829878</v>
+        <v>-0.2064235150151798</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>8064</v>
+        <v>8050</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>東捷</t>
+          <t>廣積</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>512.7588310273788</v>
+        <v>628.2425455310257</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>146</v>
+        <v>52.3</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>52.47881820139872</v>
+        <v>44.33644281878845</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>27.68556191691983</v>
+        <v>30.50847427550895</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.3687859053171408</v>
+        <v>0.4675725361014795</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-2.931194368051707</v>
+        <v>-0.9717537990353372</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>8104</v>
+        <v>8462</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>錸寶</t>
+          <t>柏文</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>508.4282197133863</v>
+        <v>628.0911587289578</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>38</v>
+        <v>143</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>46.82271812333091</v>
+        <v>54.57268588601194</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>23.42288447859709</v>
+        <v>18.95180984592917</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.1394046532513814</v>
+        <v>0.5698227149927222</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.5869942128679988</v>
+        <v>0.0610579136272663</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>8155</v>
+        <v>8093</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>博智</t>
+          <t>保銳</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>501.1626449940253</v>
+        <v>620.1520671189626</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>375</v>
+        <v>19.85</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>46.36459366107689</v>
+        <v>53.86709856800623</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>17.3153983430041</v>
+        <v>8.320865341235697</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.090089911751701</v>
+        <v>0.2621152276908852</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,11 +2266,11 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-1.441636599655132</v>
+        <v>0.2806517570627108</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -2287,7 +2287,7 @@
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>500.4376034161058</v>
+        <v>615.437603416106</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>60</v>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>57.36157442149037</v>
+        <v>57.36157445021928</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>22.68901073079778</v>
+        <v>22.68901079560497</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>0.9360921772520858</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.2061178651703252</v>
+        <v>-0.2061178650749235</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>8289</v>
+        <v>8150</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>泰藝</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>498.86096027508</v>
+        <v>610.3804510484578</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>58.6</v>
+        <v>99.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,49 +2354,49 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>42.62896676020881</v>
+        <v>53.05783183518129</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>23.28874501700983</v>
+        <v>26.61891496866733</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.364281773683163</v>
+        <v>0.746128137176377</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M36" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-1.820136208173366</v>
+        <v>-1.121885614079074</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>8150</v>
+        <v>9136</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>巨騰-DR</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>495.3804510484578</v>
+        <v>608.8717288543772</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>99.5</v>
+        <v>14.1</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>53.05783183602853</v>
+        <v>52.08360615045702</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>26.61891495703059</v>
+        <v>42.99649006280962</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.746128137176377</v>
+        <v>0.2219482871222466</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-1.121885614098161</v>
+        <v>-0.655931095345875</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>8358</v>
+        <v>8499</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>鼎炫-KY</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>492.754689486453</v>
+        <v>595.518720674526</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>600</v>
+        <v>312</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>52.53341302713674</v>
+        <v>56.12909558241354</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>19.99631813291146</v>
+        <v>17.39445751553768</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.9659786879760104</v>
+        <v>0.3200644836451023</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-13.53549253088472</v>
+        <v>0.8519404305200595</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>9906</v>
+        <v>8411</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>欣巴巴</t>
+          <t>福貞-KY</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>483.1269047451949</v>
+        <v>582.7552294481803</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>41.35</v>
+        <v>12.2</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>50.73510210581735</v>
+        <v>53.9148430890959</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>38.09203802174776</v>
+        <v>39.4428509186767</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.4276575648092571</v>
+        <v>1.204059487632845</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.5204031165412275</v>
+        <v>-0.0073356457467858</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>8499</v>
+        <v>8481</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>鼎炫-KY</t>
+          <t>政伸</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>480.5187206745259</v>
+        <v>582.3429621363663</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>312</v>
+        <v>41.6</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>56.12909556244411</v>
+        <v>52.60354957926912</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>17.39445751716094</v>
+        <v>23.13998366317458</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.3200644836451023</v>
+        <v>1.135592067988669</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.8519404307108474</v>
+        <v>-0.0416918113795829</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>8438</v>
+        <v>8067</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>昶昕</t>
+          <t>志旭</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>477.4948662990728</v>
+        <v>578.195620452093</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>96.09999999999999</v>
+        <v>13.15</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>58.34262075183361</v>
+        <v>51.07610634130555</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>23.53374940386432</v>
+        <v>7.563467526881096</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.2952465120376523</v>
+        <v>1.815086799926389</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>1.166902513678362</v>
+        <v>0.000333961491668</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>9905</v>
+        <v>8131</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>大華</t>
+          <t>福懋科</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>472.5995961598118</v>
+        <v>577.364409156485</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>21.3</v>
+        <v>72</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>64.09542070607273</v>
+        <v>51.15454128222665</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>18.90108618608365</v>
+        <v>13.79302684640228</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.523623636202851</v>
+        <v>0.5849207772849453</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.0578734691891674</v>
+        <v>-0.5502133212208264</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>8481</v>
+        <v>8932</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>政伸</t>
+          <t>智通*</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>467.3429621363662</v>
+        <v>558.1629417194875</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>41.6</v>
+        <v>108.5</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>52.60354936081112</v>
+        <v>57.41464141588462</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>23.13998368155289</v>
+        <v>19.61136769632025</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.135592067988669</v>
+        <v>0.6283346928456069</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.0416918113700404</v>
+        <v>0.657067008074486</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>8182</v>
+        <v>8476</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>加高</t>
+          <t>台境*</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>465.157572834106</v>
+        <v>555.9263169269311</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>49.1</v>
+        <v>24.75</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>52.78955736323011</v>
+        <v>90.44881082790404</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>24.17410143005826</v>
+        <v>61.51873933738428</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.4986798822405933</v>
+        <v>1.392631692693111</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.6375702523769826</v>
+        <v>0.5074302983292556</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>8234</v>
+        <v>8103</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>新漢</t>
+          <t>瀚荃</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>453.5630474231849</v>
+        <v>555.222689289198</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>71.40000000000001</v>
+        <v>98.8</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>56.83112430607277</v>
+        <v>48.50613960773495</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>19.66385884968909</v>
+        <v>17.91957445204195</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.950711994117117</v>
+        <v>0.6177943225721959</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.4925173473507046</v>
+        <v>0.3464527895137554</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>8093</v>
+        <v>8442</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>保銳</t>
+          <t>威宏-KY</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>450.1520671189632</v>
+        <v>538.6302742576554</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>19.85</v>
+        <v>40.7</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>53.86709858990735</v>
+        <v>43.66757283217989</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>8.320865352913104</v>
+        <v>21.00547615992419</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.2621152276908852</v>
+        <v>0.3939710984023096</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.2806517568501684</v>
+        <v>0.3618550935461768</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, breakout_20d, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>8068</v>
+        <v>8072</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>全達</t>
+          <t>陞泰</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>444.6318743497773</v>
+        <v>535.972416029889</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>18.95</v>
+        <v>29.3</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>43.97007183648663</v>
+        <v>51.4521511462689</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>20.05864800861288</v>
+        <v>24.42232115871372</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.3657327011830161</v>
+        <v>0.2220424777542141</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.0437844746542497</v>
+        <v>-0.0587393387952595</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>8067</v>
+        <v>8104</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>志旭</t>
+          <t>錸寶</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>438.1956204520928</v>
+        <v>528.4282197133863</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>13.15</v>
+        <v>38</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>51.07610637282391</v>
+        <v>46.82271827655048</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>7.563467582340081</v>
+        <v>23.42288447100941</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.815086799926389</v>
+        <v>0.1394046532513814</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.000333961424892</v>
+        <v>-0.5869942130110982</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>8109</v>
+        <v>8155</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>博大</t>
+          <t>博智</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>427.8597261902911</v>
+        <v>521.1626449940252</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>123.5</v>
+        <v>375</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>54.81150741834409</v>
+        <v>46.36459368673433</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>23.1335874222186</v>
+        <v>17.3153983307813</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.4401116643442047</v>
+        <v>1.090089911751701</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.0961313349467959</v>
+        <v>-1.441636599845951</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>8411</v>
+        <v>8454</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>福貞-KY</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>422.7552294481803</v>
+        <v>516.1890193455164</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>12.2</v>
+        <v>297.5</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>53.9148430890959</v>
+        <v>48.38441213547319</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>39.44285081683243</v>
+        <v>45.41615918015344</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.204059487632845</v>
+        <v>0.8276407544254143</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.0073356457563255</v>
+        <v>-11.00682117039754</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>8299</v>
+        <v>9908</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>大台北</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>421.6895504320637</v>
+        <v>514.8684453924965</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>2385</v>
+        <v>29.75</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>49.55019906218445</v>
+        <v>58.66321713834776</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>11.82155264430269</v>
+        <v>19.23850065946437</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.4384034877302947</v>
+        <v>0.4924282290704231</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-13.73207673539794</v>
+        <v>0.0207024535637217</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>8084</v>
+        <v>8064</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>巨虹</t>
+          <t>東捷</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>418.0480568991162</v>
+        <v>512.7588310273788</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>48.75</v>
+        <v>146</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>53.76500784523137</v>
+        <v>52.47881821189027</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>18.96648138439916</v>
+        <v>27.68556191691983</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.4538547012479314</v>
+        <v>0.3687859053171408</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.00019835574028</v>
+        <v>-2.931194368147114</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>8277</v>
+        <v>9907</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>商丞</t>
+          <t>統一實</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>415.544487880726</v>
+        <v>502.930557627837</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>9.98</v>
+        <v>15.15</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>52.19445619553387</v>
+        <v>33.51746545346212</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>27.79279789490716</v>
+        <v>29.96654768911989</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.2091589307233157</v>
+        <v>1.128302141436992</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.1570334172251601</v>
+        <v>-0.1200813867387775</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>8103</v>
+        <v>8464</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>瀚荃</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>415.2226892891981</v>
+        <v>501.7705757339926</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>98.8</v>
+        <v>346</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,49 +3308,49 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>48.50613961211693</v>
+        <v>53.62908975436638</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>17.91957427513231</v>
+        <v>15.62236262036001</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.6177943225721959</v>
+        <v>0.7810185825640448</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M54" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.3464527893339246</v>
+        <v>0.665949665608883</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>9908</v>
+        <v>8289</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>大台北</t>
+          <t>泰藝</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>399.8684453924965</v>
+        <v>498.86096027508</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>29.75</v>
+        <v>58.6</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>58.66321725477694</v>
+        <v>42.62896676437445</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>19.23850053652633</v>
+        <v>23.28874509091021</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.4924282290704231</v>
+        <v>0.364281773683163</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.0207024535351033</v>
+        <v>-1.820136208201982</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>8442</v>
+        <v>9902</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>威宏-KY</t>
+          <t>台火</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>398.6302742576554</v>
+        <v>493.7431919510032</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>40.7</v>
+        <v>13.75</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>43.66757266773647</v>
+        <v>48.39697854516452</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>21.00547613137932</v>
+        <v>14.44586547274484</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.3939710984023096</v>
+        <v>0.1578038408535756</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.3618550935461768</v>
+        <v>0.009348242436340101</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, kd_golden_cross, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>8932</v>
+        <v>8358</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>智通*</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>388.1629417194871</v>
+        <v>492.754689486453</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>108.5</v>
+        <v>600</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,49 +3467,49 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>57.41464133511985</v>
+        <v>52.53341303040393</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>19.61136775342576</v>
+        <v>19.99631814632365</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.6283346928456069</v>
+        <v>0.9659786879760104</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.6570670077475027</v>
+        <v>-13.53549253098006</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>8476</v>
+        <v>9906</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>台境*</t>
+          <t>欣巴巴</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>385.9263169269311</v>
+        <v>483.1269047451949</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>24.75</v>
+        <v>41.35</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>90.4488108323152</v>
+        <v>50.73510218672932</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>61.5187392614079</v>
+        <v>38.09203793514406</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.392631692693111</v>
+        <v>0.4276575648092571</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.5074302982433987</v>
+        <v>-0.5204031168274175</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>8114</v>
+        <v>8147</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>振樺電</t>
+          <t>正淩</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>375.8785627644738</v>
+        <v>482.7950107641505</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>183.5</v>
+        <v>143</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>33.21081827122704</v>
+        <v>41.35147637434058</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>22.58855592595246</v>
+        <v>22.02162863297232</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.4034363220818172</v>
+        <v>0.6865167600366107</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-4.169527910437653</v>
+        <v>-0.3057664723705784</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>8147</v>
+        <v>8438</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>正淩</t>
+          <t>昶昕</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>367.7950107641505</v>
+        <v>467.4948662990728</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>143</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>41.35147634180479</v>
+        <v>58.34262075084641</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>22.02162863297233</v>
+        <v>23.5337493687659</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.6865167600366107</v>
+        <v>0.2952465120376523</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.3057664718936026</v>
+        <v>1.166902513678362</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>8472</v>
+        <v>8068</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>夠麻吉</t>
+          <t>全達</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>364.5249420951353</v>
+        <v>464.6318743497773</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>81.7</v>
+        <v>18.95</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>48.13089765734538</v>
+        <v>43.97007185674953</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>19.64195568303482</v>
+        <v>20.05864807276787</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.7187807757049164</v>
+        <v>0.3657327011830161</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-1.077577942846312</v>
+        <v>0.0437844746828688</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>8111</v>
+        <v>9912</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>立碁</t>
+          <t>偉聯</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>355.2819846872231</v>
+        <v>456.0796132398034</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>52.2</v>
+        <v>12.4</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>34.93148043223621</v>
+        <v>43.99991543609677</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>28.20467209747382</v>
+        <v>30.26729079937139</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.5310826413591174</v>
+        <v>0.2300713760947423</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.2918338104800804</v>
+        <v>-0.0166708694079488</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>9902</v>
+        <v>8240</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>台火</t>
+          <t>華宏</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>353.7431919510001</v>
+        <v>450.8899980190933</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>13.75</v>
+        <v>53.2</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>48.39697880812685</v>
+        <v>39.19893373375644</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>14.44586545434318</v>
+        <v>15.40514257036344</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.1578038408535756</v>
+        <v>0.5477760274617386</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.0093482423409446</v>
+        <v>-0.3434826615308823</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, kd_golden_cross, williams_r_recovery</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>8462</v>
+        <v>8176</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>柏文</t>
+          <t>智捷</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>348.0911587289578</v>
+        <v>419.6850254505355</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>143</v>
+        <v>9.98</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>54.57268581418794</v>
+        <v>41.5373128621835</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>18.9518098580055</v>
+        <v>6.86239087878204</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.5698227149927222</v>
+        <v>1.630661851506915</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.0610579138180433</v>
+        <v>-0.0086511532374227</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>8390</v>
+        <v>8084</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>金益鼎</t>
+          <t>巨虹</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>344.3837500798107</v>
+        <v>418.0480568991162</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>107.5</v>
+        <v>48.75</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>43.4674485226602</v>
+        <v>53.76500785911128</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>21.66133449915919</v>
+        <v>18.96648138225485</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.4187768609338428</v>
+        <v>0.4538547012479314</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-1.763819776233597</v>
+        <v>0.0001983557498154</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>8422</v>
+        <v>8201</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>可寧衛*</t>
+          <t>無敵</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>341.4890134974041</v>
+        <v>417.9671067842728</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>27.9</v>
+        <v>13.05</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>47.5332559983264</v>
+        <v>47.11418796207657</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>13.76359993124467</v>
+        <v>18.30505395570373</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.4785949032091668</v>
+        <v>0.4095561454275258</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.1016891967387838</v>
+        <v>-0.06988780678693329</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>9912</v>
+        <v>8277</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>偉聯</t>
+          <t>商丞</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>341.0796132398034</v>
+        <v>415.544487880726</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>12.4</v>
+        <v>9.98</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>43.9999153554733</v>
+        <v>52.1944562095662</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>30.26729078746634</v>
+        <v>27.79279788124305</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.2300713760947423</v>
+        <v>0.2091589307233157</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.0166708694079488</v>
+        <v>-0.1570334172404226</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>8240</v>
+        <v>8431</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>華宏</t>
+          <t>匯鑽科</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>340.8899980190933</v>
+        <v>413.9095805048069</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>53.2</v>
+        <v>53.3</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>39.19893371770164</v>
+        <v>46.24255437123011</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>15.40514264385294</v>
+        <v>12.83121343530589</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.5477760274617386</v>
+        <v>0.5840959468367829</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.3434826616072004</v>
+        <v>0.2377313363206763</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>8271</v>
+        <v>8443</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>阿瘦</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>337.6666617370968</v>
+        <v>412.6450853111344</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>194.5</v>
+        <v>11.45</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>38.47977677926507</v>
+        <v>50.93713363613745</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>17.12955527691739</v>
+        <v>51.80304551522201</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.5001076037833055</v>
+        <v>0.441904270634919</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-2.05353288798285</v>
+        <v>0.0212857515009138</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>8488</v>
+        <v>8455</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>吉源-KY</t>
+          <t>大拓-KY</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>328.3229555967138</v>
+        <v>411.8158912824155</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>0</v>
+        <v>27.8</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>17.33668735205721</v>
+        <v>41.38577915308546</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>16.37017030935926</v>
+        <v>19.51748688965262</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0</v>
+        <v>0.1712022971207231</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.6918087731658142</v>
+        <v>-0.7033794994034959</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>8086</v>
+        <v>8213</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>志超</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>325.2938976640796</v>
+        <v>408.5393013917906</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>149.5</v>
+        <v>36.65</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>46.5342965475657</v>
+        <v>48.58635433100392</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>17.75061142317906</v>
+        <v>11.60636404908049</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.5865974312792517</v>
+        <v>0.4214075342552613</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-1.798745729792878</v>
+        <v>-0.0077572194832879</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>8074</v>
+        <v>8114</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>鉅橡</t>
+          <t>振樺電</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>325.1475300255701</v>
+        <v>405.8785627644738</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>70.3</v>
+        <v>183.5</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>46.37156448265385</v>
+        <v>33.2108183950433</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>10.4048388792256</v>
+        <v>22.58855587560209</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.6101398188984638</v>
+        <v>0.4034363220818172</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.4531604990266338</v>
+        <v>-4.169527910437653</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>9103</v>
+        <v>8410</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>美德醫療-DR</t>
+          <t>森田</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>322.8392349848555</v>
+        <v>403.1157429646667</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>5.18</v>
+        <v>33.3</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>45.14299543179541</v>
+        <v>44.31107129692982</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>21.95453198924729</v>
+        <v>20.72686379223427</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.3080151005251685</v>
+        <v>0.5192291754188922</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.0622099670333526</v>
+        <v>0.0301698939604448</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>8176</v>
+        <v>8374</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>智捷</t>
+          <t>羅昇</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>304.6850254505355</v>
+        <v>393.4315191424997</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>9.98</v>
+        <v>85</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>41.53731242244222</v>
+        <v>40.54547769206789</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>6.862390895151625</v>
+        <v>15.14101016080284</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>1.630661851506915</v>
+        <v>0.2529224381595566</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.008651153227884199</v>
+        <v>-1.15509710306939</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>8431</v>
+        <v>8940</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>匯鑽科</t>
+          <t>新天地</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>303.9095805048069</v>
+        <v>384.0750067109617</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>53.3</v>
+        <v>16.45</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>46.24255435896573</v>
+        <v>43.42480293121259</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>12.83121343530588</v>
+        <v>16.46066575965989</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.5840959468367829</v>
+        <v>0.3425601358434733</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.2377313363588347</v>
+        <v>0.0091853089405965</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>8201</v>
+        <v>8367</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>無敵</t>
+          <t>建新國際</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>302.9671067842728</v>
+        <v>377.8023555305648</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>13.05</v>
+        <v>40.35</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>47.11418798233833</v>
+        <v>43.55717518924462</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>18.30505392278659</v>
+        <v>22.72414678075421</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.4095561454275258</v>
+        <v>2.075317384676116</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.06988780679647311</v>
+        <v>0.0484788334067291</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>8477</v>
+        <v>8111</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>創業家</t>
+          <t>立碁</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>300.5105289141906</v>
+        <v>375.2819846872231</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>16.55</v>
+        <v>52.2</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>45.22968877817945</v>
+        <v>34.93148036742376</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>22.33132397191234</v>
+        <v>28.20467200682826</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.734822566200422</v>
+        <v>0.5310826413591174</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.2593268751116411</v>
+        <v>-0.2918338101366524</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>9930</v>
+        <v>8080</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>中聯資源</t>
+          <t>永利聯合</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>291.3602306948191</v>
+        <v>372.3308070651519</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>66.3</v>
+        <v>27.75</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>30.86300340384086</v>
+        <v>46.21683781788526</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>23.41299988210012</v>
+        <v>46.64555159532989</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.5223726093041829</v>
+        <v>0.686069915908277</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.3729917335477367</v>
+        <v>-0.0077861095893745</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>8374</v>
+        <v>8210</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>羅昇</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>283.4315191424997</v>
+        <v>366.9261399101521</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>85</v>
+        <v>1285</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,49 +4633,49 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>40.5454776547185</v>
+        <v>45.46562331539484</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>15.1410100801708</v>
+        <v>17.09193396905096</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.2529224381595566</v>
+        <v>0.4713491064770964</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L79" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M79" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-1.155097102783211</v>
+        <v>-23.76132565279553</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>8443</v>
+        <v>8472</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>阿瘦</t>
+          <t>夠麻吉</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>277.6450853111343</v>
+        <v>364.5249420951353</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>11.45</v>
+        <v>81.7</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>50.93713358587751</v>
+        <v>48.13089767680453</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>51.80304549122479</v>
+        <v>19.64195563147002</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.441904270634919</v>
+        <v>0.7187807757049164</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.0212857515009138</v>
+        <v>-1.077577942932183</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>8455</v>
+        <v>8422</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>大拓-KY</t>
+          <t>可寧衛*</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>276.8158912824156</v>
+        <v>361.4890134974041</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>27.8</v>
+        <v>27.9</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,49 +4739,49 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>41.38577921211769</v>
+        <v>47.53325582050073</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>19.51748680861811</v>
+        <v>13.76359996796944</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.1712022971207231</v>
+        <v>0.4785949032091668</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L81" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M81" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.7033794997183069</v>
+        <v>-0.1016891962482989</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>8213</v>
+        <v>8089</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>志超</t>
+          <t>康全電訊</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>273.5393013917906</v>
+        <v>354.1714566301104</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>36.65</v>
+        <v>20.15</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>48.58635430113458</v>
+        <v>46.16081122502227</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>11.60636403872273</v>
+        <v>30.93476576070704</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.4214075342552613</v>
+        <v>0.3124448162527812</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.0077572194737398</v>
+        <v>-0.1032241904077553</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>8076</v>
+        <v>8087</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>伍豐</t>
+          <t>華鎂鑫</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>271.6724189232996</v>
+        <v>351.666267609713</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>24.55</v>
+        <v>33</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>43.5761072835013</v>
+        <v>45.24389599418802</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>16.57581035018794</v>
+        <v>13.97617967645338</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.1868282506684978</v>
+        <v>0.1959394241483865</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.3239906040950718</v>
+        <v>-0.1973634690075038</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>8102</v>
+        <v>8074</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>傑霖科技</t>
+          <t>鉅橡</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>271.3410725283653</v>
+        <v>345.1475300255701</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>69</v>
+        <v>70.3</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>47.18281230057797</v>
+        <v>46.37156448764706</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>12.27879781109242</v>
+        <v>10.40483889969466</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.1350615214658489</v>
+        <v>0.6101398188984638</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.7744250324480091</v>
+        <v>-0.4531604990361779</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>8048</v>
+        <v>8390</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>德勝</t>
+          <t>金益鼎</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>269.5133692510225</v>
+        <v>344.3837500798107</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>63.8</v>
+        <v>107.5</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>50.48686095420714</v>
+        <v>43.46744853496514</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>16.22007851483257</v>
+        <v>21.66133451902</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.4140402402509173</v>
+        <v>0.4187768609338428</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.3563164908377506</v>
+        <v>-1.76381977638623</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>8940</v>
+        <v>8487</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>新天地</t>
+          <t>愛爾達-創</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>269.0750067109618</v>
+        <v>343.5412276113167</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>16.45</v>
+        <v>78.8</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>43.42480269376269</v>
+        <v>47.84121669995859</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>16.46066576155906</v>
+        <v>11.85854297074631</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.3425601358434733</v>
+        <v>0.2435998839937778</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.009185309074149699</v>
+        <v>-0.2404340164659286</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>9907</v>
+        <v>8171</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>統一實</t>
+          <t>天宇</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>267.930557627837</v>
+        <v>343.1287129810356</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>15.15</v>
+        <v>21.6</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>33.51746589974138</v>
+        <v>45.26834611357516</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>29.96654713395681</v>
+        <v>20.21247497531951</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.128302141436992</v>
+        <v>0.3465074175247374</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.1200813870822081</v>
+        <v>-0.08377474545911021</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>8410</v>
+        <v>8271</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>森田</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>263.1157429646667</v>
+        <v>337.6666617370968</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>33.3</v>
+        <v>194.5</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>44.31107122963753</v>
+        <v>38.47977679806039</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>20.72686379223427</v>
+        <v>17.12955525480974</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.5192291754188922</v>
+        <v>0.5001076037833055</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.0301698939986061</v>
+        <v>-2.053532887868383</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>8367</v>
+        <v>8059</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>建新國際</t>
+          <t>凱碩</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>262.8023555305647</v>
+        <v>332.7208511773773</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>40.35</v>
+        <v>16.65</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>43.55717499995841</v>
+        <v>34.88702096947341</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>22.72414677706805</v>
+        <v>20.55600466279593</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>2.075317384676116</v>
+        <v>0.2870530852966192</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.0484788334735019</v>
+        <v>-0.113639627948909</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>8080</v>
+        <v>8488</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>永利聯合</t>
+          <t>吉源-KY</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>257.3308070651519</v>
+        <v>328.3229555967138</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>27.75</v>
+        <v>0</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>46.21683781788526</v>
+        <v>17.3366873594118</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>46.64555171213512</v>
+        <v>16.37017030230856</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.686069915908277</v>
+        <v>0</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.0077861095893745</v>
+        <v>-0.691808773156275</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>8210</v>
+        <v>8086</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>251.9261399101522</v>
+        <v>325.2938976640796</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>1285</v>
+        <v>149.5</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>45.46562329593378</v>
+        <v>46.53429655915108</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>17.09193394664818</v>
+        <v>17.7506113356804</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.4713491064770964</v>
+        <v>0.5865974312792517</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-23.76132565193686</v>
+        <v>-1.798745729792878</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>8464</v>
+        <v>9103</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>美德醫療-DR</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>246.7705757339925</v>
+        <v>322.8392349848555</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>346</v>
+        <v>5.18</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>53.62908973393299</v>
+        <v>45.1429954170974</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>15.62236261671953</v>
+        <v>21.95453208596757</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.7810185825640448</v>
+        <v>0.3080151005251685</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.6659496671352176</v>
+        <v>-0.0622099670257207</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>8341</v>
+        <v>9910</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>日友</t>
+          <t>豐泰</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>244.4996905783951</v>
+        <v>304.2451926103748</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>75.90000000000001</v>
+        <v>70</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>37.49933319794629</v>
+        <v>41.98098662841728</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>23.09701905112858</v>
+        <v>19.85308495593974</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.4872979521507792</v>
+        <v>0.3330924661124502</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.5798071977774747</v>
+        <v>-1.366647764904786</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>8089</v>
+        <v>8477</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>康全電訊</t>
+          <t>創業家</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>239.1714566301104</v>
+        <v>300.5105289141906</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>20.15</v>
+        <v>16.55</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>46.16081063482285</v>
+        <v>45.22968868885533</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>30.93476562039275</v>
+        <v>22.33132417412057</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.3124448162527812</v>
+        <v>0.734822566200422</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.1032241898735284</v>
+        <v>-0.2593268750257831</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>8092</v>
+        <v>9955</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>建暐</t>
+          <t>佳龍</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>238.0552956719765</v>
+        <v>300.3539986345023</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>13.4</v>
+        <v>26.4</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>27.26144536826763</v>
+        <v>39.27423136965532</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>19.72489719580033</v>
+        <v>24.00136848644752</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>1.07749937756049</v>
+        <v>0.5021431173685375</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.1406065261594848</v>
+        <v>-0.0056221025849054</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>8487</v>
+        <v>9110</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>愛爾達-創</t>
+          <t>越南控-DR</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>228.5412276113168</v>
+        <v>291.8285651358949</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>78.8</v>
+        <v>3.29</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>47.84121667024189</v>
+        <v>51.77109164904274</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>11.85854280935106</v>
+        <v>16.02447749389453</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.2435998839937778</v>
+        <v>0.2258002986506055</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.2404340164468411</v>
+        <v>-0.0690559759829044</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>8059</v>
+        <v>9930</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>凱碩</t>
+          <t>中聯資源</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>217.7208511773774</v>
+        <v>291.3602306948191</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>16.65</v>
+        <v>66.3</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>34.88702062949552</v>
+        <v>30.86300341891296</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>20.55600453426968</v>
+        <v>23.4129999709987</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.2870530852966192</v>
+        <v>0.5223726093041829</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.1136396279966106</v>
+        <v>-0.3729917333187846</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>8087</v>
+        <v>8102</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>華鎂鑫</t>
+          <t>傑霖科技</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>211.6662676097129</v>
+        <v>291.3410725283653</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>45.24389599418802</v>
+        <v>47.18281230057797</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>13.97617966745773</v>
+        <v>12.27879785193197</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.1959394241483865</v>
+        <v>0.1350615214658489</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.1973634690075038</v>
+        <v>-0.7744250324670832</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>9904</v>
+        <v>9911</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>寶成</t>
+          <t>櫻花</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>191.2929670065048</v>
+        <v>279.3925529323971</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>25.35</v>
+        <v>82.8</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>37.31156306108262</v>
+        <v>46.83401752950857</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>15.52622771367128</v>
+        <v>11.42340268288193</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1.188126476754322</v>
+        <v>0.8451907155180818</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.0961086177055368</v>
+        <v>-0.0496010119361667</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>9910</v>
+        <v>8076</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>豐泰</t>
+          <t>伍豐</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>189.245192610375</v>
+        <v>271.6724189232996</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>70</v>
+        <v>24.55</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>41.9809865920616</v>
+        <v>43.57610737924975</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>19.85308465672956</v>
+        <v>16.57581032361512</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.3330924661124502</v>
+        <v>0.1868282506684978</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-1.366647765000199</v>
+        <v>-0.3239906040473708</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>9955</v>
+        <v>8048</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>佳龍</t>
+          <t>德勝</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>185.3539986345017</v>
+        <v>269.5133692510225</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>26.4</v>
+        <v>63.8</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>39.2742312539961</v>
+        <v>50.48686096708746</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>24.00136837728891</v>
+        <v>16.22007864165231</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.5021431173685375</v>
+        <v>0.4140402402509173</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.0056221023464121</v>
+        <v>-0.3563164908759094</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>8171</v>
+        <v>8341</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>天宇</t>
+          <t>日友</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>183.1287129810356</v>
+        <v>264.4996905783951</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>21.6</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>45.26834612120819</v>
+        <v>37.49933329086947</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>20.21247494134462</v>
+        <v>23.09701911216801</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.3465074175247374</v>
+        <v>0.4872979521507792</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,7 +5870,7 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.08377474545911021</v>
+        <v>-0.5798071977774747</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
@@ -5880,21 +5880,21 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>8249</v>
+        <v>8423</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>菱光</t>
+          <t>保綠-KY</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>176.2272436555841</v>
+        <v>258.2780619653417</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>47.2</v>
+        <v>17.7</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>37.24088308501772</v>
+        <v>47.1517590949456</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>18.53286376944171</v>
+        <v>10.0697708736452</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.4160013510739867</v>
+        <v>0.8303523582669102</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.6508818252932875</v>
+        <v>-0.0034056160381864</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>8467</v>
+        <v>8478</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>波力-KY</t>
+          <t>東哥遊艇</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>160.6023917395396</v>
+        <v>254.7145455617791</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>118</v>
+        <v>151.5</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>48.25119238042321</v>
+        <v>45.51637131178826</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>11.61936427406996</v>
+        <v>12.35237001246438</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.5842792247958174</v>
+        <v>0.3644078392598067</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>1.067902839834879</v>
+        <v>-0.0127000366708314</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>9802</v>
+        <v>8404</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>鈺齊-KY</t>
+          <t>百和興業-KY</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>150.1340993106713</v>
+        <v>246.4113107373592</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>72.7</v>
+        <v>16.65</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>36.67140554281949</v>
+        <v>46.84097275440556</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>16.59567189721919</v>
+        <v>12.51086343777298</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.586053750276566</v>
+        <v>0.5610304235678193</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.5781018310520409</v>
+        <v>-0.0381070685749237</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>8085</v>
+        <v>8440</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>福華</t>
+          <t>綠電</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>144.6691014906409</v>
+        <v>243.3825654382446</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>12</v>
+        <v>21.65</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>44.17519925228195</v>
+        <v>44.06834820957548</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>18.2371785529405</v>
+        <v>11.29587113665714</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.3928704207019167</v>
+        <v>0.2693555311061644</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.1332355848369814</v>
+        <v>-0.1180638074039066</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>8423</v>
+        <v>8092</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>保綠-KY</t>
+          <t>建暐</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>143.2780619653417</v>
+        <v>238.0552956719765</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>17.7</v>
+        <v>13.4</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>47.15175883190923</v>
+        <v>27.26144526974045</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>10.0697708736452</v>
+        <v>19.72489757292635</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.8303523582669102</v>
+        <v>1.07749937756049</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.0034056160095701</v>
+        <v>-0.1406065260640867</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>8478</v>
+        <v>8463</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>東哥遊艇</t>
+          <t>潤泰材</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>139.7145455617789</v>
+        <v>211.6019261587936</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>151.5</v>
+        <v>21.35</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>45.51637114829695</v>
+        <v>42.06553514934242</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>12.3523700666505</v>
+        <v>14.66234407879238</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.3644078392598067</v>
+        <v>0.5266618239434016</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.0127000365754255</v>
+        <v>-0.0525905929299887</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>9911</v>
+        <v>9904</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>櫻花</t>
+          <t>寶成</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>139.3925529323971</v>
+        <v>191.2929670065048</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>82.8</v>
+        <v>25.35</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>46.83401755730322</v>
+        <v>37.31156292776836</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>11.42340265318765</v>
+        <v>15.52622780511601</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.8451907155180818</v>
+        <v>1.188126476754322</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.0496010118598531</v>
+        <v>-0.09610861758152441</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>8101</v>
+        <v>8249</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>華冠</t>
+          <t>菱光</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>137.9604598005752</v>
+        <v>176.2272436555841</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>12.6</v>
+        <v>47.2</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>37.62086159919154</v>
+        <v>37.24088311815545</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>13.43684537690746</v>
+        <v>18.53286376546734</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>2.737756714060032</v>
+        <v>0.4160013510739867</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.2848976887407983</v>
+        <v>-0.6508818252360491</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>8440</v>
+        <v>8467</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>綠電</t>
+          <t>波力-KY</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>128.3825654382446</v>
+        <v>160.6023917395396</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>21.65</v>
+        <v>118</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>44.06834805996304</v>
+        <v>48.25119240057258</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>11.29587116891601</v>
+        <v>11.61936426867609</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.2693555311061644</v>
+        <v>0.5842792247958174</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.1180638072798885</v>
+        <v>1.067902839834879</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>8429</v>
+        <v>9802</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>金麗-KY</t>
+          <t>鈺齊-KY</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>116.0742357396029</v>
+        <v>150.1340993106707</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>6.18</v>
+        <v>72.7</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>36.46042054416633</v>
+        <v>36.67140569924649</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>19.14346434764355</v>
+        <v>16.59567188385032</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.2876975244726877</v>
+        <v>0.586053750276566</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.0492821402316958</v>
+        <v>-0.5781018308994131</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>8404</v>
+        <v>8085</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>百和興業-KY</t>
+          <t>福華</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>111.4113107373591</v>
+        <v>144.6691014906409</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>16.65</v>
+        <v>12</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>46.84097275440556</v>
+        <v>44.17519949221388</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>12.51086332703744</v>
+        <v>18.23717859562397</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.5610304235678193</v>
+        <v>0.3928704207019167</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.038107068632162</v>
+        <v>-0.1332355850659343</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>8463</v>
+        <v>8101</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>潤泰材</t>
+          <t>華冠</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>96.60192615879356</v>
+        <v>137.9604598005753</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>21.35</v>
+        <v>12.6</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>42.06553502503807</v>
+        <v>37.62086170396216</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>14.66234413444808</v>
+        <v>13.43684531674256</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.5266618239434016</v>
+        <v>2.737756714060032</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.0525905929299887</v>
+        <v>-0.2848976889411333</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>9110</v>
+        <v>8429</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>越南控-DR</t>
+          <t>金麗-KY</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>91.82856513589496</v>
+        <v>116.0742357396029</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>3.29</v>
+        <v>6.18</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,16 +6541,16 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>51.77109165016939</v>
+        <v>36.46042047018683</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>16.02447754589672</v>
+        <v>19.14346449794094</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.2258002986506055</v>
+        <v>0.2876975244726877</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
@@ -6559,11 +6559,11 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.0690559759867202</v>
+        <v>-0.0492821402030772</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
